--- a/esyluban/examples/dev/DataTables/test/demos.xlsx
+++ b/esyluban/examples/dev/DataTables/test/demos.xlsx
@@ -628,9 +628,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="H3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -834,7 +834,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1122,6 +1122,31 @@
           <t>id</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>reward_item_id</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>reward_item_count</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -1380,9 +1405,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1481,7 +1506,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1834,10 +1859,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D2:G2"/>
     <mergeCell ref="I3:L3"/>
+    <mergeCell ref="I4:L4"/>
     <mergeCell ref="D3:G3"/>
-    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2008,9 +2033,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="C4:K4"/>
     <mergeCell ref="L3:N3"/>
-    <mergeCell ref="C2:K2"/>
     <mergeCell ref="C3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2519,8 +2544,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="J3:O3"/>
   </mergeCells>
@@ -2956,9 +2981,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E4:G4"/>
     <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H4:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
